--- a/diseño_3d/mecanismos/comprobacion_curvas_matlab/puntos_curva_CATIA.xlsx
+++ b/diseño_3d/mecanismos/comprobacion_curvas_matlab/puntos_curva_CATIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apolinar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD3547ED-06F1-4D6F-9B39-E0FE52D019B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE197DEB-02F1-41A8-86E2-2857759998CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{043BECAB-8E86-4ED1-844D-614EF801B465}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9F662288-08E4-4A71-B51A-1928EC8E0360}"/>
   </bookViews>
   <sheets>
     <sheet name="Muestreo CATIA" sheetId="1" r:id="rId1"/>
@@ -446,7 +446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AC36F10-CFA6-4AC7-B826-91185E6EE5BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501C7089-B909-4DB8-B990-CEF27CE5701D}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
